--- a/data/trans_orig/P6716-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P6716-Clase-trans_orig.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W46"/>
+  <dimension ref="A1:W40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si hablan con entusiasmo de su empresa a otras personas en 2012</t>
+          <t>Población según si hablan con entusiasmo de su empresa a otras personas en 2012 (tasa de respuesta: 99,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10073</t>
+          <t>9791</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8919</t>
+          <t>9724</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3698</t>
+          <t>3731</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14463</t>
+          <t>16393</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1874</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10964</t>
+          <t>10854</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>966</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12940</t>
+          <t>12259</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3917</t>
+          <t>3864</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16435</t>
+          <t>17023</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35294</t>
+          <t>35235</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>62163</t>
+          <t>61248</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11937</t>
+          <t>11973</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30717</t>
+          <t>29919</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>52036</t>
+          <t>50329</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>85835</t>
+          <t>83432</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>16,78%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37714</t>
+          <t>38497</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64541</t>
+          <t>64176</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27263</t>
+          <t>27388</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50228</t>
+          <t>51965</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>70134</t>
+          <t>70193</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>107176</t>
+          <t>107326</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,59%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>178215</t>
+          <t>178108</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>213365</t>
+          <t>212878</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>113905</t>
+          <t>114012</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>142280</t>
+          <t>142093</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>303274</t>
+          <t>304466</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>348027</t>
+          <t>347576</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>69,9%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10791</t>
+          <t>11570</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11842</t>
+          <t>11065</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4550</t>
+          <t>4560</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17730</t>
+          <t>17191</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2874</t>
+          <t>2798</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16377</t>
+          <t>14958</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>928</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8229</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4826</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18241</t>
+          <t>20089</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24094</t>
+          <t>25212</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47063</t>
+          <t>48696</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>27662</t>
+          <t>27367</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>51035</t>
+          <t>49307</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>55527</t>
+          <t>57407</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>88562</t>
+          <t>89878</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,17%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>54256</t>
+          <t>53529</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85114</t>
+          <t>83316</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35062</t>
+          <t>34776</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59951</t>
+          <t>59176</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>96696</t>
+          <t>94518</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>136109</t>
+          <t>133495</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,44%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>124580</t>
+          <t>126638</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>159930</t>
+          <t>161774</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>61640</t>
+          <t>61863</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>88705</t>
+          <t>88724</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>196489</t>
+          <t>196778</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>238864</t>
+          <t>242498</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>57,12%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9370</t>
+          <t>9304</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7413</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10169</t>
+          <t>11372</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3011</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14575</t>
+          <t>14186</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1054</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12037</t>
+          <t>11471</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>5453</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19300</t>
+          <t>19853</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>33665</t>
+          <t>34150</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>57400</t>
+          <t>59497</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11097</t>
+          <t>10410</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25900</t>
+          <t>26382</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>48657</t>
+          <t>48917</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>78262</t>
+          <t>78385</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,04%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>63412</t>
+          <t>60743</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>91723</t>
+          <t>90116</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12931</t>
+          <t>13155</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28936</t>
+          <t>29142</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>79782</t>
+          <t>78791</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>113347</t>
+          <t>113588</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,04%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>131252</t>
+          <t>130451</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>165831</t>
+          <t>166001</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>57733</t>
+          <t>57517</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>77765</t>
+          <t>78665</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>198293</t>
+          <t>195657</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>237262</t>
+          <t>236726</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>60,53%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4326</t>
+          <t>4997</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18830</t>
+          <t>19778</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7178</t>
+          <t>6659</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20785</t>
+          <t>21846</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13335</t>
+          <t>14266</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33728</t>
+          <t>33630</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17565</t>
+          <t>16564</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>37007</t>
+          <t>35436</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8623</t>
+          <t>8922</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>23969</t>
+          <t>25246</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>28892</t>
+          <t>26887</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>52888</t>
+          <t>55142</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>79745</t>
+          <t>81104</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>116416</t>
+          <t>117405</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>65874</t>
+          <t>64942</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>97226</t>
+          <t>96517</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>153217</t>
+          <t>156234</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>201024</t>
+          <t>201648</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,79%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>99471</t>
+          <t>100672</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>138364</t>
+          <t>139979</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>59252</t>
+          <t>58508</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>87509</t>
+          <t>88414</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>168835</t>
+          <t>169842</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>219047</t>
+          <t>219709</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,28%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>153839</t>
+          <t>153772</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>195502</t>
+          <t>194714</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>101112</t>
+          <t>101664</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>135537</t>
+          <t>135835</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>264636</t>
+          <t>265541</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>318039</t>
+          <t>318542</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,9%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9742</t>
+          <t>9750</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>25329</t>
+          <t>26337</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>12289</t>
+          <t>12372</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>13763</t>
+          <t>15163</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>33280</t>
+          <t>34238</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,45%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8698</t>
+          <t>8178</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>25094</t>
+          <t>24179</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>9835</t>
+          <t>10352</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>27537</t>
+          <t>27912</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>21873</t>
+          <t>22042</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>45351</t>
+          <t>45509</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,89%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>24043</t>
+          <t>23622</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>44255</t>
+          <t>44203</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>37853</t>
+          <t>37329</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>63286</t>
+          <t>61395</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>34,96%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>66754</t>
+          <t>65971</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>100511</t>
+          <t>99783</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,46%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>27184</t>
+          <t>28025</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>49105</t>
+          <t>50421</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>34908</t>
+          <t>36074</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>60468</t>
+          <t>60017</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>68668</t>
+          <t>68506</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>101698</t>
+          <t>102175</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,19%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>38068</t>
+          <t>37835</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>61579</t>
+          <t>60947</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>42542</t>
+          <t>44219</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>68753</t>
+          <t>69153</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>89147</t>
+          <t>88344</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>125110</t>
+          <t>122921</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>37,53%</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4121,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4131,107 +4131,107 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>37</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>39203</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>28253</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>53669</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>28497</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19180</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>39206</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>65</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>67701</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>53669</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>84912</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -4244,107 +4244,107 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>55</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>59285</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>45153</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>76745</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>43557</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>31361</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>58554</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>93</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>102841</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>84513</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>126858</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -4357,107 +4357,107 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>244</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>256855</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>228258</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>288581</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>187</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>204294</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>177522</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>231237</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>431</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>461149</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>422586</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>496707</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,99%</t>
         </is>
       </c>
     </row>
@@ -4470,107 +4470,107 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>333</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>351462</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>320767</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>384439</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>214</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>223944</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>198333</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>249894</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>547</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>575406</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>535456</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>617638</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,1%</t>
         </is>
       </c>
     </row>
@@ -4583,107 +4583,107 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>664</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>712947</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>675599</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>751415</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>407</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>446062</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>412159</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>476624</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1159009</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1112674</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1208325</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,07%</t>
         </is>
       </c>
     </row>
@@ -4696,804 +4696,121 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1419752</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1419752</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1419752</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>874</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>946354</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>946354</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>946354</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2207</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2366106</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2366106</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2366106</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>Nunca</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>39203</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>28242</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>53801</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>2,76%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>3,79%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>28497</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>19354</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>39692</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>2,05%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>4,19%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>67701</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>52219</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>87120</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="W40" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n"/>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Solo alguna vez</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>59285</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>45346</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>77012</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>4,18%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>5,42%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>43557</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>31284</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>57676</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>4,6%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>6,09%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>102841</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>83702</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>125829</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>4,35%</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
-      <c r="W41" s="2" t="inlineStr">
-        <is>
-          <t>5,32%</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n"/>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Algunas veces</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>256855</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>226886</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>285938</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>18,09%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>15,98%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>20,14%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>204294</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>179451</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>231325</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>21,59%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>18,96%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>24,44%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>431</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>461149</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>423210</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>508088</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>19,49%</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>17,89%</t>
-        </is>
-      </c>
-      <c r="W42" s="2" t="inlineStr">
-        <is>
-          <t>21,47%</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n"/>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Muchas veces</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>333</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>351462</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>317329</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>390213</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>24,76%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>22,35%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>27,48%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>223944</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>200005</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>253605</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>23,66%</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>21,13%</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>26,8%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>547</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>575406</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>532829</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>621080</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>24,32%</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>22,52%</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t>26,25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n"/>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>Siempre</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>664</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>712947</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>671257</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>753581</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>50,22%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>47,28%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>53,08%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>407</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>446062</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>413153</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>475492</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>47,13%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>43,66%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>50,24%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>1071</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>1159009</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>1111012</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t>1208422</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t>48,98%</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>46,96%</t>
-        </is>
-      </c>
-      <c r="W44" s="2" t="inlineStr">
-        <is>
-          <t>51,07%</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="n"/>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>1333</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>1419752</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>1419752</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>1419752</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>874</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>946354</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>946354</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>946354</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t>2207</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>2366106</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>2366106</t>
-        </is>
-      </c>
-      <c r="T45" s="2" t="inlineStr">
-        <is>
-          <t>2366106</t>
-        </is>
-      </c>
-      <c r="U45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A22:A27"/>
-    <mergeCell ref="A40:A45"/>
     <mergeCell ref="A4:A9"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A34:A39"/>
@@ -5513,7 +4830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W46"/>
+  <dimension ref="A1:W40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5544,7 +4861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si hablan con entusiasmo de su empresa a otras personas en 2016</t>
+          <t>Población según si hablan con entusiasmo de su empresa a otras personas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5744,7 +5061,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>9745</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5759,7 +5076,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5774,12 +5091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12124</t>
+          <t>12778</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5794,7 +5111,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5809,12 +5126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3016</t>
+          <t>2568</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17917</t>
+          <t>15844</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5824,12 +5141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>5029</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19698</t>
+          <t>18888</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5867,12 +5184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5887,12 +5204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10731</t>
+          <t>10001</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5907,7 +5224,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5922,12 +5239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7439</t>
+          <t>7845</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22964</t>
+          <t>24094</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5937,12 +5254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5282,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29273</t>
+          <t>28402</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>54423</t>
+          <t>54077</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5980,12 +5297,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6000,12 +5317,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20806</t>
+          <t>22314</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>42014</t>
+          <t>43101</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6015,12 +5332,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6035,12 +5352,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>56760</t>
+          <t>55390</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>89683</t>
+          <t>89013</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6050,12 +5367,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,07%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +5395,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46338</t>
+          <t>46883</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>76024</t>
+          <t>77198</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6093,12 +5410,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6113,12 +5430,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30863</t>
+          <t>31084</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54680</t>
+          <t>54422</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6128,12 +5445,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6148,12 +5465,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>84698</t>
+          <t>84193</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>119665</t>
+          <t>120677</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6163,12 +5480,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,5%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +5508,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>147493</t>
+          <t>144878</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>181770</t>
+          <t>181142</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6206,12 +5523,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,31%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6226,12 +5543,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>117514</t>
+          <t>118016</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>145889</t>
+          <t>146197</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6241,12 +5558,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6261,12 +5578,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>276642</t>
+          <t>276582</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>320864</t>
+          <t>320230</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6276,12 +5593,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>65,02%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +5738,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3621</t>
+          <t>3065</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16494</t>
+          <t>16068</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6436,12 +5753,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6456,12 +5773,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3666</t>
+          <t>3326</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14943</t>
+          <t>14896</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6471,12 +5788,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6491,12 +5808,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8682</t>
+          <t>8646</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25392</t>
+          <t>25024</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6511,7 +5828,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +5851,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2223</t>
+          <t>3173</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14564</t>
+          <t>14969</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6549,12 +5866,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6569,12 +5886,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11454</t>
+          <t>11400</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28626</t>
+          <t>28173</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6584,12 +5901,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6604,12 +5921,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>17937</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>37489</t>
+          <t>39183</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6619,12 +5936,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +5964,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>44758</t>
+          <t>44553</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>74663</t>
+          <t>72390</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6662,12 +5979,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6682,12 +5999,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>40734</t>
+          <t>39161</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>63691</t>
+          <t>63670</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6697,12 +6014,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6717,12 +6034,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>89910</t>
+          <t>90942</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>129126</t>
+          <t>127854</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6732,12 +6049,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,51%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6077,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51095</t>
+          <t>51371</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>79946</t>
+          <t>81735</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6775,12 +6092,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6795,12 +6112,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36687</t>
+          <t>36498</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59144</t>
+          <t>60254</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6810,12 +6127,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6830,12 +6147,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>95384</t>
+          <t>94511</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>129856</t>
+          <t>130755</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6845,12 +6162,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>30,18%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6190,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>90517</t>
+          <t>91702</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>122992</t>
+          <t>123082</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6888,12 +6205,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,09%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6908,12 +6225,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51459</t>
+          <t>51520</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>79065</t>
+          <t>79034</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6923,12 +6240,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6943,12 +6260,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>149520</t>
+          <t>150105</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>191374</t>
+          <t>194075</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6958,12 +6275,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>44,8%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +6420,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3916</t>
+          <t>3722</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18191</t>
+          <t>18139</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7118,12 +6435,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7138,12 +6455,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7153,12 +6470,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7173,12 +6490,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4308</t>
+          <t>4300</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18532</t>
+          <t>18827</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7193,7 +6510,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +6533,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6083</t>
+          <t>6185</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20952</t>
+          <t>20705</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7231,12 +6548,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7256,7 +6573,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4799</t>
+          <t>4443</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7271,7 +6588,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7286,12 +6603,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6202</t>
+          <t>6449</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21907</t>
+          <t>21551</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7301,12 +6618,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +6646,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30982</t>
+          <t>29511</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>54874</t>
+          <t>54613</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7344,12 +6661,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7364,12 +6681,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>903</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8980</t>
+          <t>8306</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7379,12 +6696,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7399,12 +6716,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>33347</t>
+          <t>33214</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>57805</t>
+          <t>59663</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7414,12 +6731,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,97%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +6759,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>53038</t>
+          <t>52670</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>79684</t>
+          <t>80422</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7457,12 +6774,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7477,12 +6794,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13673</t>
+          <t>14367</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29688</t>
+          <t>29933</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7492,12 +6809,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7512,12 +6829,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>71935</t>
+          <t>71380</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>102408</t>
+          <t>101395</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7527,12 +6844,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>35,64%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +6872,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>75885</t>
+          <t>75409</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>105057</t>
+          <t>104472</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7570,12 +6887,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7590,12 +6907,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>33454</t>
+          <t>32808</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>49815</t>
+          <t>48984</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7605,12 +6922,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7625,12 +6942,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>114203</t>
+          <t>113092</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>148161</t>
+          <t>148164</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7640,7 +6957,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -7785,12 +7102,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10413</t>
+          <t>10401</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28762</t>
+          <t>28035</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7805,7 +7122,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7820,12 +7137,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6927</t>
+          <t>7007</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21648</t>
+          <t>20968</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7835,12 +7152,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7855,12 +7172,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20447</t>
+          <t>21526</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>43223</t>
+          <t>42591</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7870,12 +7187,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -7898,12 +7215,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>22619</t>
+          <t>22963</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>45164</t>
+          <t>46361</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7913,12 +7230,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7933,12 +7250,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>14321</t>
+          <t>14474</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>32560</t>
+          <t>32242</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7948,12 +7265,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7968,12 +7285,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>40298</t>
+          <t>41117</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>69764</t>
+          <t>70090</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7983,12 +7300,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -8011,12 +7328,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>98279</t>
+          <t>96455</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>136683</t>
+          <t>136288</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8026,12 +7343,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8046,12 +7363,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>84321</t>
+          <t>84810</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>119435</t>
+          <t>118473</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8061,12 +7378,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8081,12 +7398,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>191002</t>
+          <t>194018</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>241338</t>
+          <t>243428</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8096,12 +7413,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,41%</t>
         </is>
       </c>
     </row>
@@ -8124,12 +7441,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>136873</t>
+          <t>136957</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>178852</t>
+          <t>178415</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8139,12 +7456,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8159,12 +7476,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>97120</t>
+          <t>95569</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>130832</t>
+          <t>130259</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8174,12 +7491,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8194,12 +7511,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>244723</t>
+          <t>242607</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>298949</t>
+          <t>297081</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8209,12 +7526,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,67%</t>
         </is>
       </c>
     </row>
@@ -8237,12 +7554,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>144985</t>
+          <t>144271</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>186077</t>
+          <t>188144</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8252,12 +7569,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8272,12 +7589,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>102119</t>
+          <t>100183</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>136440</t>
+          <t>137550</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8287,12 +7604,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8307,12 +7624,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>256807</t>
+          <t>258902</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>311016</t>
+          <t>312465</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8322,12 +7639,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,47%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +7784,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6127</t>
+          <t>5720</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>21334</t>
+          <t>20875</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8482,12 +7799,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8502,12 +7819,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>14534</t>
+          <t>14440</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>32982</t>
+          <t>32151</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8517,12 +7834,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8537,12 +7854,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>24053</t>
+          <t>25071</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>48070</t>
+          <t>47576</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8552,12 +7869,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,15%</t>
         </is>
       </c>
     </row>
@@ -8580,12 +7897,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>13168</t>
+          <t>12812</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>32298</t>
+          <t>31289</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8595,12 +7912,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8615,12 +7932,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>12382</t>
+          <t>13083</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>29408</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8630,12 +7947,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8650,12 +7967,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>29126</t>
+          <t>30066</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>53860</t>
+          <t>53560</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8665,12 +7982,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,68%</t>
         </is>
       </c>
     </row>
@@ -8693,12 +8010,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>50254</t>
+          <t>49128</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>76630</t>
+          <t>77487</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8708,12 +8025,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8728,12 +8045,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>42889</t>
+          <t>44325</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>70248</t>
+          <t>70283</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8743,12 +8060,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8763,12 +8080,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>102782</t>
+          <t>101362</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>138170</t>
+          <t>137255</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8778,12 +8095,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>35,05%</t>
         </is>
       </c>
     </row>
@@ -8806,12 +8123,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>34025</t>
+          <t>33430</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>57488</t>
+          <t>58098</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8821,12 +8138,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8841,12 +8158,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>38587</t>
+          <t>38434</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>62984</t>
+          <t>63393</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8856,12 +8173,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8876,12 +8193,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>78696</t>
+          <t>77572</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>112275</t>
+          <t>113567</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8891,12 +8208,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>29,0%</t>
         </is>
       </c>
     </row>
@@ -8919,12 +8236,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>39911</t>
+          <t>39799</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>65016</t>
+          <t>66568</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8934,12 +8251,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8954,12 +8271,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>38428</t>
+          <t>39197</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>63127</t>
+          <t>62359</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8969,12 +8286,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8989,12 +8306,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>85946</t>
+          <t>84643</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>119395</t>
+          <t>119378</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9004,7 +8321,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -9129,7 +8446,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -9139,107 +8456,107 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>49355</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>34807</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>64592</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>47858</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>35987</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>63404</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>87</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>97213</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>76383</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>118177</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -9252,107 +8569,107 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>82695</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>65926</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>103171</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>66098</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>51374</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>81295</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>139</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>148792</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>126530</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>175637</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -9365,107 +8682,107 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>288</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>317423</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>285020</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>346451</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>238</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>244633</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>217349</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>273563</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>526</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>562056</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>520639</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>605833</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,64%</t>
         </is>
       </c>
     </row>
@@ -9478,107 +8795,107 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>376</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>393457</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>361422</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>429420</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>271</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>272025</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>248469</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>301804</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>647</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>665481</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>620999</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>709256</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,85%</t>
         </is>
       </c>
     </row>
@@ -9591,107 +8908,107 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>542</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>579393</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>542482</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>615831</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>394</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>405606</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>373166</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>436007</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>936</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>984999</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>934103</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1033228</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>42,03%</t>
         </is>
       </c>
     </row>
@@ -9704,804 +9021,121 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1422322</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1422322</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1422322</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1036219</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1036219</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1036219</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2458541</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2458541</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2458541</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>Nunca</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>49355</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>35206</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>66203</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>4,65%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>47858</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>34899</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>63104</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>4,62%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>3,37%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>6,09%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>97213</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>77755</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>119556</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>3,95%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
-        </is>
-      </c>
-      <c r="W40" s="2" t="inlineStr">
-        <is>
-          <t>4,86%</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n"/>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Solo alguna vez</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>82695</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>66251</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>103824</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>5,81%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>4,66%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>7,3%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>66098</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>51595</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>81829</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>6,38%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>4,98%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>7,9%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>148792</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>126223</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>174065</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>6,05%</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>5,13%</t>
-        </is>
-      </c>
-      <c r="W41" s="2" t="inlineStr">
-        <is>
-          <t>7,08%</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n"/>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Algunas veces</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>317423</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>285785</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>351781</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>22,32%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>20,09%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>24,73%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>244633</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>218747</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>274328</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>23,61%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>21,11%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>26,47%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>526</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>562056</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>524247</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>607668</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>22,86%</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>21,32%</t>
-        </is>
-      </c>
-      <c r="W42" s="2" t="inlineStr">
-        <is>
-          <t>24,72%</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n"/>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Muchas veces</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>376</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>393457</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>361713</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>432494</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>27,66%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>25,43%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>30,41%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>272025</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>246451</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>303095</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>26,25%</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>23,78%</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>29,25%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>665481</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>619313</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>710599</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>27,07%</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>25,19%</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t>28,9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n"/>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>Siempre</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>542</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>579393</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>538483</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>617169</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>40,74%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>37,86%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>43,39%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>394</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>405606</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>375523</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>438894</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>39,14%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>36,24%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>42,36%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>936</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>984999</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>934483</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t>1032040</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t>40,06%</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>38,01%</t>
-        </is>
-      </c>
-      <c r="W44" s="2" t="inlineStr">
-        <is>
-          <t>41,98%</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="n"/>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>1323</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>1422322</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>1422322</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>1422322</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>1012</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>1036219</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>1036219</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>1036219</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t>2335</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>2458541</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>2458541</t>
-        </is>
-      </c>
-      <c r="T45" s="2" t="inlineStr">
-        <is>
-          <t>2458541</t>
-        </is>
-      </c>
-      <c r="U45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A22:A27"/>
-    <mergeCell ref="A40:A45"/>
     <mergeCell ref="A4:A9"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A34:A39"/>

--- a/data/trans_orig/P6716-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P6716-Clase-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1241</t>
+          <t>934</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9791</t>
+          <t>9750</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>8993</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3731</t>
+          <t>3666</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16393</t>
+          <t>15365</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>1887</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10854</t>
+          <t>11656</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>966</t>
+          <t>949</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12259</t>
+          <t>10512</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3864</t>
+          <t>4058</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17023</t>
+          <t>17461</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35235</t>
+          <t>34911</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>61248</t>
+          <t>61063</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11973</t>
+          <t>11309</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29919</t>
+          <t>30334</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>50329</t>
+          <t>51897</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>83432</t>
+          <t>84087</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,91%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38497</t>
+          <t>37453</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64176</t>
+          <t>62636</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27388</t>
+          <t>27390</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51965</t>
+          <t>49868</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>70193</t>
+          <t>69561</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>107326</t>
+          <t>106314</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,38%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>178108</t>
+          <t>180110</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>212878</t>
+          <t>214367</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>114012</t>
+          <t>115293</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>142093</t>
+          <t>142490</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>304466</t>
+          <t>302085</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>347576</t>
+          <t>348265</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>70,04%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11570</t>
+          <t>11235</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>1891</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11065</t>
+          <t>10871</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17191</t>
+          <t>17579</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2798</t>
+          <t>2721</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14958</t>
+          <t>15369</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>946</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>8553</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>4832</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>20089</t>
+          <t>18996</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25212</t>
+          <t>24076</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48696</t>
+          <t>47832</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>27367</t>
+          <t>26831</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>49307</t>
+          <t>49249</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>57407</t>
+          <t>57195</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>89878</t>
+          <t>89176</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,0%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53529</t>
+          <t>54891</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83316</t>
+          <t>85616</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34776</t>
+          <t>34994</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59176</t>
+          <t>58656</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>94518</t>
+          <t>96555</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>133495</t>
+          <t>135939</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>32,02%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>126638</t>
+          <t>125558</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>161774</t>
+          <t>160336</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>61863</t>
+          <t>62232</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>88724</t>
+          <t>89359</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>196778</t>
+          <t>197329</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>242498</t>
+          <t>240303</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>56,6%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9304</t>
+          <t>10406</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>5482</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11372</t>
+          <t>11310</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3130</t>
+          <t>2847</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14186</t>
+          <t>13393</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11471</t>
+          <t>10555</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5453</t>
+          <t>5883</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19853</t>
+          <t>20683</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>34150</t>
+          <t>33868</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>59497</t>
+          <t>57938</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10410</t>
+          <t>10274</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>26382</t>
+          <t>25564</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>48917</t>
+          <t>49554</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>78385</t>
+          <t>78594</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,1%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>60743</t>
+          <t>61132</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>90116</t>
+          <t>91094</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13155</t>
+          <t>13119</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29142</t>
+          <t>29338</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>78791</t>
+          <t>79622</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>113588</t>
+          <t>112405</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>28,74%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>130451</t>
+          <t>132356</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>166001</t>
+          <t>165730</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>57517</t>
+          <t>56688</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>78665</t>
+          <t>77676</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>195657</t>
+          <t>197028</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>236726</t>
+          <t>236885</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>60,57%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4997</t>
+          <t>4873</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19778</t>
+          <t>19903</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6659</t>
+          <t>6675</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21846</t>
+          <t>20218</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14266</t>
+          <t>14456</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33630</t>
+          <t>33844</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>16564</t>
+          <t>16516</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>35436</t>
+          <t>35986</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8922</t>
+          <t>8993</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>25246</t>
+          <t>25973</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>26887</t>
+          <t>28528</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>55142</t>
+          <t>55356</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>81104</t>
+          <t>81048</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>117405</t>
+          <t>115195</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>64942</t>
+          <t>65825</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>96517</t>
+          <t>97174</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>156234</t>
+          <t>153921</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>201648</t>
+          <t>202170</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,86%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>100672</t>
+          <t>102425</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>139979</t>
+          <t>140089</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>58508</t>
+          <t>59835</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>88414</t>
+          <t>88967</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>169842</t>
+          <t>169653</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>219709</t>
+          <t>214972</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>29,62%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>153772</t>
+          <t>156605</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>194714</t>
+          <t>195218</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>101664</t>
+          <t>101982</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>135835</t>
+          <t>135928</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>265541</t>
+          <t>264316</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>318542</t>
+          <t>319738</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>44,06%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9750</t>
+          <t>9705</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>26337</t>
+          <t>26039</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2053</t>
+          <t>2584</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>12372</t>
+          <t>13219</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>15163</t>
+          <t>14928</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>34238</t>
+          <t>33525</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8178</t>
+          <t>8328</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>24179</t>
+          <t>25210</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10352</t>
+          <t>10472</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>27912</t>
+          <t>27667</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>22042</t>
+          <t>23137</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>45509</t>
+          <t>45001</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,74%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>23622</t>
+          <t>23914</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>44203</t>
+          <t>44511</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>37329</t>
+          <t>38766</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>61395</t>
+          <t>62523</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>65971</t>
+          <t>66056</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>99783</t>
+          <t>99524</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,38%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>28025</t>
+          <t>26932</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>50421</t>
+          <t>49150</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>36074</t>
+          <t>35357</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>60017</t>
+          <t>59528</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>68506</t>
+          <t>70534</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>102175</t>
+          <t>101181</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>30,89%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>37835</t>
+          <t>35898</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>60947</t>
+          <t>60513</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>44219</t>
+          <t>44613</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>69153</t>
+          <t>69071</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>88344</t>
+          <t>88330</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>122921</t>
+          <t>123589</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,73%</t>
         </is>
       </c>
     </row>
@@ -4141,12 +4141,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>28253</t>
+          <t>28572</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>53669</t>
+          <t>53200</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>19180</t>
+          <t>19235</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>39206</t>
+          <t>40920</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>53669</t>
+          <t>52659</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>84912</t>
+          <t>86170</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>45153</t>
+          <t>44425</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>76745</t>
+          <t>76411</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>31361</t>
+          <t>31638</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>58554</t>
+          <t>58356</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>84513</t>
+          <t>82827</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>126858</t>
+          <t>126259</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>228258</t>
+          <t>228725</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>288581</t>
+          <t>290790</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>177522</t>
+          <t>179181</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>231237</t>
+          <t>232405</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>422586</t>
+          <t>424898</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>496707</t>
+          <t>506140</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>320767</t>
+          <t>321746</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>384439</t>
+          <t>386097</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>198333</t>
+          <t>196910</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>249894</t>
+          <t>250654</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>535456</t>
+          <t>534020</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>617638</t>
+          <t>617194</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,08%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>675599</t>
+          <t>672895</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>751415</t>
+          <t>751637</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>412159</t>
+          <t>413914</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>476624</t>
+          <t>477932</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1112674</t>
+          <t>1107715</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1208325</t>
+          <t>1209447</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>51,12%</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9745</t>
+          <t>10102</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1189</t>
+          <t>1199</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12778</t>
+          <t>12751</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2568</t>
+          <t>3168</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15844</t>
+          <t>15780</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>5177</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18888</t>
+          <t>18890</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5184,7 +5184,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>949</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>9004</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7845</t>
+          <t>8333</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24094</t>
+          <t>24213</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28402</t>
+          <t>28722</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>54077</t>
+          <t>54890</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22314</t>
+          <t>22390</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43101</t>
+          <t>43434</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>55390</t>
+          <t>56086</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>89013</t>
+          <t>89316</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,13%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46883</t>
+          <t>46522</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77198</t>
+          <t>74109</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31084</t>
+          <t>30563</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54422</t>
+          <t>54882</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>84193</t>
+          <t>83247</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>120677</t>
+          <t>122396</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,85%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>144878</t>
+          <t>147317</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>181142</t>
+          <t>181971</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>118016</t>
+          <t>118511</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>146197</t>
+          <t>147837</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>276582</t>
+          <t>272392</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>320230</t>
+          <t>319542</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>64,88%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3065</t>
+          <t>3012</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16068</t>
+          <t>14905</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3326</t>
+          <t>3221</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14896</t>
+          <t>16028</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8646</t>
+          <t>8655</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25024</t>
+          <t>26128</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3173</t>
+          <t>3039</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14969</t>
+          <t>13992</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11400</t>
+          <t>11759</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28173</t>
+          <t>29797</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5901,47 +5901,47 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
+          <t>6,22%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>15,75%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>26118</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>16575</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>39092</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
           <t>6,03%</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>14,89%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>26118</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>17937</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>39183</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>6,03%</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>44553</t>
+          <t>44556</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>72390</t>
+          <t>72246</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>39161</t>
+          <t>39813</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>63670</t>
+          <t>63845</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>90942</t>
+          <t>91622</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>127854</t>
+          <t>128793</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,73%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51371</t>
+          <t>52677</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81735</t>
+          <t>80755</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36498</t>
+          <t>37175</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60254</t>
+          <t>60431</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>94511</t>
+          <t>94149</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>130755</t>
+          <t>131987</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,47%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>91702</t>
+          <t>90060</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>123082</t>
+          <t>123713</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51520</t>
+          <t>50534</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>79034</t>
+          <t>79017</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>150105</t>
+          <t>150392</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>194075</t>
+          <t>191540</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,21%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3722</t>
+          <t>3582</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18139</t>
+          <t>18329</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4300</t>
+          <t>3829</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18827</t>
+          <t>17658</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6185</t>
+          <t>5683</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20705</t>
+          <t>19836</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4443</t>
+          <t>3684</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6449</t>
+          <t>6432</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21551</t>
+          <t>21305</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>29511</t>
+          <t>30651</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>54613</t>
+          <t>54472</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>903</t>
+          <t>920</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8306</t>
+          <t>9106</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>33214</t>
+          <t>33837</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>59663</t>
+          <t>59145</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,79%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52670</t>
+          <t>53356</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>80422</t>
+          <t>80028</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14367</t>
+          <t>15046</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29933</t>
+          <t>30345</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>71380</t>
+          <t>72689</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>101395</t>
+          <t>103106</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>36,25%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>75409</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>104472</t>
+          <t>106193</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>32808</t>
+          <t>32859</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>48984</t>
+          <t>48250</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>113092</t>
+          <t>116003</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>148164</t>
+          <t>149256</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>52,47%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10401</t>
+          <t>10227</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28035</t>
+          <t>26739</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7007</t>
+          <t>7015</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20968</t>
+          <t>20993</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7152,7 +7152,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>21526</t>
+          <t>21396</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>42591</t>
+          <t>43455</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>22963</t>
+          <t>21610</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>46361</t>
+          <t>45271</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>14474</t>
+          <t>13780</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>32242</t>
+          <t>32962</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>41117</t>
+          <t>41267</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>70090</t>
+          <t>70030</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>96455</t>
+          <t>95945</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>136288</t>
+          <t>134722</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>84810</t>
+          <t>84673</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>118473</t>
+          <t>119146</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>194018</t>
+          <t>192334</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>243428</t>
+          <t>243570</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,43%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>136957</t>
+          <t>137780</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>178415</t>
+          <t>181217</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>95569</t>
+          <t>96747</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>130259</t>
+          <t>131159</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>242607</t>
+          <t>242788</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>297081</t>
+          <t>298743</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,87%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>144271</t>
+          <t>141801</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>188144</t>
+          <t>185036</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>100183</t>
+          <t>100710</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>137550</t>
+          <t>136748</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>258902</t>
+          <t>254257</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>312465</t>
+          <t>309589</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,13%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5720</t>
+          <t>5681</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>20875</t>
+          <t>20264</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>14440</t>
+          <t>13717</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>32151</t>
+          <t>31790</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>25071</t>
+          <t>23823</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>47576</t>
+          <t>47711</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -7897,12 +7897,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>12812</t>
+          <t>12941</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>31289</t>
+          <t>31922</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7912,12 +7912,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7932,12 +7932,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>13083</t>
+          <t>12747</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>30451</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7947,12 +7947,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7967,12 +7967,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>30066</t>
+          <t>30595</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>53560</t>
+          <t>54882</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7982,12 +7982,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>14,02%</t>
         </is>
       </c>
     </row>
@@ -8010,12 +8010,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>49128</t>
+          <t>50390</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>77487</t>
+          <t>77826</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8025,12 +8025,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8045,12 +8045,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>44325</t>
+          <t>43779</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>70283</t>
+          <t>67891</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>101362</t>
+          <t>103203</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>137255</t>
+          <t>137644</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,15%</t>
         </is>
       </c>
     </row>
@@ -8123,12 +8123,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>33430</t>
+          <t>34167</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>58098</t>
+          <t>57702</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8138,12 +8138,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8158,12 +8158,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>38434</t>
+          <t>38223</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>63393</t>
+          <t>61811</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>77572</t>
+          <t>76712</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>113567</t>
+          <t>110455</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>28,21%</t>
         </is>
       </c>
     </row>
@@ -8236,12 +8236,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>39799</t>
+          <t>40387</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>66568</t>
+          <t>66248</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8251,12 +8251,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8271,12 +8271,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>39197</t>
+          <t>38911</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>62359</t>
+          <t>61846</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8306,12 +8306,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>84643</t>
+          <t>85421</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>119378</t>
+          <t>120984</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,9%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>34807</t>
+          <t>36604</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>64592</t>
+          <t>68722</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>35987</t>
+          <t>34954</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>63404</t>
+          <t>62768</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>76383</t>
+          <t>78929</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>118177</t>
+          <t>118635</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -8579,12 +8579,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>65926</t>
+          <t>65818</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>103171</t>
+          <t>102946</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8594,12 +8594,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8614,12 +8614,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>51374</t>
+          <t>51494</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>81295</t>
+          <t>83338</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8649,12 +8649,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>126530</t>
+          <t>124986</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>175637</t>
+          <t>174392</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -8692,12 +8692,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>285020</t>
+          <t>283049</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>346451</t>
+          <t>351058</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8707,12 +8707,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8727,12 +8727,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>217349</t>
+          <t>214977</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>273563</t>
+          <t>272109</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8762,12 +8762,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>520639</t>
+          <t>524892</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>605833</t>
+          <t>610116</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,82%</t>
         </is>
       </c>
     </row>
@@ -8805,12 +8805,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>361422</t>
+          <t>359859</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>429420</t>
+          <t>427779</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8820,12 +8820,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>248469</t>
+          <t>246968</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>301804</t>
+          <t>300639</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8875,12 +8875,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>620999</t>
+          <t>618380</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>709256</t>
+          <t>709148</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,84%</t>
         </is>
       </c>
     </row>
@@ -8918,12 +8918,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>542482</t>
+          <t>541249</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>615831</t>
+          <t>618291</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8933,12 +8933,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8953,12 +8953,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>373166</t>
+          <t>372341</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>436007</t>
+          <t>440483</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>934103</t>
+          <t>930225</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1033228</t>
+          <t>1037662</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>42,21%</t>
         </is>
       </c>
     </row>
